--- a/dataset_t6_grouped/results2/G3/G3_T6156_W0055F0002T0006Z000C1N63_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T6156_W0055F0002T0006Z000C1N63_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>10.40584367073783</v>
+        <v>1.690949596494898</v>
       </c>
       <c r="D2" t="n">
-        <v>3.670358772243944</v>
+        <v>0.5964333004896408</v>
       </c>
       <c r="E2" t="n">
-        <v>13.1435085516516</v>
+        <v>2.135820139643385</v>
       </c>
       <c r="F2" t="n">
-        <v>15.78515513218282</v>
+        <v>2.565087708979708</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>20.91001724434037</v>
+        <v>3.39787780220531</v>
       </c>
       <c r="D3" t="n">
-        <v>21.19071510142053</v>
+        <v>3.443491203980837</v>
       </c>
       <c r="E3" t="n">
-        <v>13.1435085516516</v>
+        <v>2.135820139643385</v>
       </c>
       <c r="F3" t="n">
-        <v>15.78515513218282</v>
+        <v>2.565087708979708</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>46.28283817061193</v>
+        <v>7.520961202724439</v>
       </c>
       <c r="D4" t="n">
-        <v>46.33322814247456</v>
+        <v>7.529149573152116</v>
       </c>
       <c r="E4" t="n">
-        <v>13.1435085516516</v>
+        <v>2.135820139643385</v>
       </c>
       <c r="F4" t="n">
-        <v>15.78515513218282</v>
+        <v>2.565087708979708</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>29.62243477459793</v>
+        <v>4.813645650872164</v>
       </c>
       <c r="D5" t="n">
-        <v>33.86003377133785</v>
+        <v>5.5022554878424</v>
       </c>
       <c r="E5" t="n">
-        <v>13.1435085516516</v>
+        <v>2.135820139643385</v>
       </c>
       <c r="F5" t="n">
-        <v>15.78515513218282</v>
+        <v>2.565087708979708</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
